--- a/Calendario-EP-2026-2.xlsx
+++ b/Calendario-EP-2026-2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
@@ -271,7 +271,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C97"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.94"/>
   </cols>
@@ -827,8 +827,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.72"/>
   </cols>
@@ -871,6 +871,18 @@
         <f aca="false">H1+7</f>
         <v>46084</v>
       </c>
+      <c r="K1" s="7" t="n">
+        <f aca="false">I1+7</f>
+        <v>46087</v>
+      </c>
+      <c r="L1" s="7" t="n">
+        <f aca="false">J1+7</f>
+        <v>46091</v>
+      </c>
+      <c r="M1" s="7" t="n">
+        <f aca="false">K1+7</f>
+        <v>46094</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
@@ -897,6 +909,9 @@
       <c r="H2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I2" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
@@ -923,6 +938,9 @@
       <c r="H3" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I3" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
@@ -949,6 +967,9 @@
       <c r="H4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I4" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
@@ -975,6 +996,9 @@
       <c r="H5" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I5" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
@@ -1001,6 +1025,9 @@
       <c r="H6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I6" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
@@ -1027,6 +1054,9 @@
       <c r="H7" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I7" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
@@ -1051,6 +1081,9 @@
         <v>1</v>
       </c>
       <c r="H8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <v>1</v>
       </c>
     </row>
